--- a/logs/merge_failed.xlsx
+++ b/logs/merge_failed.xlsx
@@ -424,10 +424,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="94" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PERAWATAN PINTU PERLINTASAN JPL BNR BOP-BTT 24-07-2026.pdf</t>
+          <t>PERAWATAN PDSE BTT 09-01-2025.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,14 +462,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31 04:09:44</t>
+          <t>2026-09-24 07:24:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PERAWATAN PTPP JPL BNR BOP-BTT 24-07-2026.pdf</t>
+          <t>PERAWATAN PDSE BTT 23-01-2025.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -479,7 +479,1095 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-31 04:10:00</t>
+          <t>2026-09-24 07:24:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PERAWATAN POINT LOCK W81 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:24:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PERAWATAN POINT LOCK W81 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:24:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W11 CLT 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W11 CLT 17-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W11 MSG 05-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W11 MSG 19-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 CLT 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 CLT 17-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 MSG 05-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W13 MSG 19-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21 CLT 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21 CLT 17-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21 MSG 05-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21 MSG 19-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21A BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21A BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21B1 BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21B1 BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21B2 BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W21B2 BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23 CLT 03-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23 CLT 17-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23 MSG 05-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23 MSG 19-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23A BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23A BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23B BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W23B BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W25 BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W25 BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W27A BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W27A BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W27B BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W27B BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31A BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31A BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31B BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31B BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31D BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31D BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31E BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W31E BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W41 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W41 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W43 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W43 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47A BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47A BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47C BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47C BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47D BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W47D BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W51A1 BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W51A1 BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W61A1 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W51A2 BOO 01-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W61A1 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W51A2 BOO 15-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W61A2 BOO 02-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W61A2 BOO 16-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W67 BOP 04-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PERAWATAN WESEL W67 BOP 18-01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>failed: no matching edited photos found in 04_photos_edited; output Tim cannot be determined</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:25:07</t>
         </is>
       </c>
     </row>
